--- a/nautilus-dcf/NAUT_DCF_Model.xlsx
+++ b/nautilus-dcf/NAUT_DCF_Model.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="168" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;$&quot;0.00"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +87,12 @@
       <i val="1"/>
       <color rgb="00767676"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="009E9E9E"/>
+      <sz val="7.5"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -203,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -239,25 +245,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -266,37 +275,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -311,13 +320,13 @@
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="17" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -335,7 +344,7 @@
     <xf numFmtId="169" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -704,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G37"/>
+  <dimension ref="B2:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1126,8 +1135,15 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="12" customHeight="1">
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Francisco Rodriguez  |  Financial Modeling Portfolio  |  github.com/Azyo1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B19:G19"/>
@@ -1137,6 +1153,7 @@
     <mergeCell ref="B31:G31"/>
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B39:G39"/>
     <mergeCell ref="B25:G25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1149,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D61"/>
+  <dimension ref="B1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1173,7 +1190,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -1190,130 +1207,130 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>EAP grants + 1 paying customer (management guidance ~$500K)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="15" t="n">
         <v>2027</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>~8 instrument shipments @ $1M ASP + early consumable pull-through</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="15" t="n">
         <v>2028</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>~25 cumulative instruments; consumables ramp to ~40% of revenue</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="15" t="n">
         <v>2029</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>~55 cumulative instruments; pharma early adopters begin conversion</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>130</v>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>~100 cumulative instruments; consumables majority of revenue</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="15" t="n">
         <v>2031</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>~145 instruments; second-gen assays launch; biopharma contracts</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="15" t="n">
         <v>2032</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>280</v>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>~190 instruments; Voyager 2.0 broadscale platform contribution</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="15" t="n">
         <v>2033</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>360</v>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>~240 instruments; international expansion</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="15" t="n">
         <v>2034</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>430</v>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>~280 instruments; mature ramp</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="15" t="n">
         <v>2035</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>490</v>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>~310 instruments; terminal-year revenue (base case)</t>
         </is>
@@ -1327,7 +1344,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -1344,130 +1361,130 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Mostly service/grant revenue; no COGS on instrument shipments</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="15" t="n">
         <v>2027</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Instrument-heavy mix (low-margin hardware); limited consumables</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="14" t="n">
+      <c r="B20" s="15" t="n">
         <v>2028</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="18" t="n">
         <v>0.52</v>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Modest consumable pull-through improvement</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="14" t="n">
+      <c r="B21" s="15" t="n">
         <v>2029</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="18" t="n">
         <v>0.55</v>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Consumables approach 40% of mix; margin inflection begins</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="14" t="n">
+      <c r="B22" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C22" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Consumables become majority; platform economies of scale</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="15" t="n">
         <v>2031</v>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C23" s="18" t="n">
         <v>0.63</v>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>Razor/blade model maturing; software/data layer contribution</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="14" t="n">
+      <c r="B24" s="15" t="n">
         <v>2032</v>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="18" t="n">
         <v>0.65</v>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>Scale gross margins; consistent with 10x Genomics / Illumina</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="14" t="n">
+      <c r="B25" s="15" t="n">
         <v>2033</v>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="18" t="n">
         <v>0.65</v>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Stable at scale</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="15" t="n">
         <v>2034</v>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="18" t="n">
         <v>0.65</v>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Stable at scale</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="15" t="n">
         <v>2035</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="18" t="n">
         <v>0.65</v>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Terminal gross margin</t>
         </is>
@@ -1481,7 +1498,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -1498,150 +1515,150 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>50.0  |  28.0</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>2026E mgmt guidance ~$77-80M total opex; phased hiring</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="15" t="n">
         <v>2027</v>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>55.0  |  30.0</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Headcount ramp for commercial launch support</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="15" t="n">
         <v>2028</v>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>60.0  |  32.0</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Second-gen probe library development</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="15" t="n">
         <v>2029</v>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>65.0  |  34.0</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Platform expansion R&amp;D; commercial scale sales team</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="14" t="n">
+      <c r="B35" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>70.0  |  36.0</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Broadscale platform R&amp;D begins</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="14" t="n">
+      <c r="B36" s="15" t="n">
         <v>2031</v>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>72.0  |  38.0</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>R&amp;D growth moderates as % of revenue</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="14" t="n">
+      <c r="B37" s="15" t="n">
         <v>2032</v>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>74.0  |  40.0</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Approaching operating leverage inflection</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="15" t="n">
         <v>2033</v>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>76.0  |  40.0</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Stable G&amp;A; R&amp;D grows modestly</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="14" t="n">
+      <c r="B39" s="15" t="n">
         <v>2034</v>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>78.0  |  41.0</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>Mature stage opex structure</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="14" t="n">
+      <c r="B40" s="15" t="n">
         <v>2035</v>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>80.0  |  42.0</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Terminal-year opex</t>
         </is>
@@ -1660,10 +1677,10 @@
           <t>Risk-Free Rate (10-yr UST)</t>
         </is>
       </c>
-      <c r="C43" s="17" t="n">
+      <c r="C43" s="18" t="n">
         <v>0.045</v>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>March 2026 10-year Treasury yield</t>
         </is>
@@ -1675,10 +1692,10 @@
           <t>Equity Risk Premium</t>
         </is>
       </c>
-      <c r="C44" s="17" t="n">
+      <c r="C44" s="18" t="n">
         <v>0.055</v>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>Damodaran US ERP</t>
         </is>
@@ -1690,10 +1707,10 @@
           <t>Beta (relevered)</t>
         </is>
       </c>
-      <c r="C45" s="15" t="n">
+      <c r="C45" s="16" t="n">
         <v>1.8</v>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>Pre-commercial tools/biotech; Seer Bio / QSI avg ~1.8</t>
         </is>
@@ -1705,10 +1722,10 @@
           <t>Size &amp; Illiquidity Premium</t>
         </is>
       </c>
-      <c r="C46" s="17" t="n">
+      <c r="C46" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Pre-revenue micro-cap; standard for development-stage co</t>
         </is>
@@ -1720,10 +1737,10 @@
           <t>Cost of Equity (Base WACC)</t>
         </is>
       </c>
-      <c r="C47" s="17" t="n">
+      <c r="C47" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>4.5% + 1.8×5.5% + 5.0% = ~20.0%; all-equity structure</t>
         </is>
@@ -1735,10 +1752,10 @@
           <t>Bull Case WACC</t>
         </is>
       </c>
-      <c r="C48" s="17" t="n">
+      <c r="C48" s="18" t="n">
         <v>0.17</v>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>De-risked scenario post commercial launch</t>
         </is>
@@ -1750,10 +1767,10 @@
           <t>Bear Case WACC</t>
         </is>
       </c>
-      <c r="C49" s="17" t="n">
+      <c r="C49" s="18" t="n">
         <v>0.23</v>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>Elevated execution risk; further delays</t>
         </is>
@@ -1765,10 +1782,10 @@
           <t>Terminal EV/Revenue (Base)</t>
         </is>
       </c>
-      <c r="C50" s="15" t="n">
+      <c r="C50" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>Mature tools co comps: Illumina ~8x, Bruker ~6x</t>
         </is>
@@ -1780,10 +1797,10 @@
           <t>Terminal EV/Revenue (Bull)</t>
         </is>
       </c>
-      <c r="C51" s="15" t="n">
+      <c r="C51" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>High-growth tools premium (10x Genomics peak)</t>
         </is>
@@ -1795,10 +1812,10 @@
           <t>Terminal EV/Revenue (Bear)</t>
         </is>
       </c>
-      <c r="C52" s="15" t="n">
+      <c r="C52" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>Discount for delayed commercialization</t>
         </is>
@@ -1810,10 +1827,10 @@
           <t>Projection Period (years)</t>
         </is>
       </c>
-      <c r="C53" s="19" t="n">
+      <c r="C53" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>FY2026E – FY2035E</t>
         </is>
@@ -1825,10 +1842,10 @@
           <t>Tax Rate</t>
         </is>
       </c>
-      <c r="C54" s="17" t="n">
+      <c r="C54" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>Applied only when EBIT &gt; 0; NOL carryforward ignored</t>
         </is>
@@ -1847,10 +1864,10 @@
           <t>Cash &amp; Equivalents ($M)</t>
         </is>
       </c>
-      <c r="C57" s="15" t="n">
+      <c r="C57" s="16" t="n">
         <v>12.4</v>
       </c>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>FY2025 10-K</t>
         </is>
@@ -1862,10 +1879,10 @@
           <t>Short-Term Investments ($M)</t>
         </is>
       </c>
-      <c r="C58" s="15" t="n">
+      <c r="C58" s="16" t="n">
         <v>91</v>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>FY2025 10-K</t>
         </is>
@@ -1877,10 +1894,10 @@
           <t>Long-Term Investments ($M)</t>
         </is>
       </c>
-      <c r="C59" s="15" t="n">
+      <c r="C59" s="16" t="n">
         <v>52.7</v>
       </c>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>FY2025 10-K</t>
         </is>
@@ -1892,10 +1909,10 @@
           <t>Total Net Cash ($M)</t>
         </is>
       </c>
-      <c r="C60" s="15" t="n">
+      <c r="C60" s="16" t="n">
         <v>156.1</v>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>Liquid assets; no material debt</t>
         </is>
@@ -1907,19 +1924,27 @@
           <t>Shares Outstanding (M)</t>
         </is>
       </c>
-      <c r="C61" s="15" t="n">
+      <c r="C61" s="16" t="n">
         <v>126.6</v>
       </c>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>FY2025 10-K weighted avg</t>
         </is>
       </c>
     </row>
+    <row r="63" ht="12" customHeight="1">
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Francisco Rodriguez  |  Financial Modeling Portfolio  |  github.com/Azyo1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="B29:D29"/>
@@ -1935,7 +1960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L23"/>
+  <dimension ref="B1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1960,7 +1985,7 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Year / Metric</t>
         </is>
@@ -2029,89 +2054,89 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="20" t="n">
+      <c r="E4" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" s="21" t="n">
         <v>130</v>
       </c>
-      <c r="H4" s="20" t="n">
+      <c r="H4" s="21" t="n">
         <v>200</v>
       </c>
-      <c r="I4" s="20" t="n">
+      <c r="I4" s="21" t="n">
         <v>280</v>
       </c>
-      <c r="J4" s="20" t="n">
+      <c r="J4" s="21" t="n">
         <v>360</v>
       </c>
-      <c r="K4" s="20" t="n">
+      <c r="K4" s="21" t="n">
         <v>430</v>
       </c>
-      <c r="L4" s="20" t="n">
+      <c r="L4" s="21" t="n">
         <v>490</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  YoY Growth %</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>1500.0%</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>275.0%</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>133.3%</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>85.7%</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>53.8%</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t>28.6%</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>19.4%</t>
         </is>
       </c>
-      <c r="L5" s="22" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>14.0%</t>
         </is>
@@ -2123,71 +2148,71 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="21" t="n">
         <v>0.3</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="21" t="n">
         <v>15.6</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="21" t="n">
         <v>38.5</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="21" t="n">
         <v>78</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="21" t="n">
         <v>126</v>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="I6" s="21" t="n">
         <v>182</v>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="J6" s="21" t="n">
         <v>234</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="K6" s="21" t="n">
         <v>279.5</v>
       </c>
-      <c r="L6" s="20" t="n">
+      <c r="L6" s="21" t="n">
         <v>318.5</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Gross Margin %</t>
         </is>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="24" t="n">
         <v>0.6</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="24" t="n">
         <v>0.52</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="24" t="n">
         <v>0.55</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="24" t="n">
         <v>0.6</v>
       </c>
-      <c r="H7" s="23" t="n">
+      <c r="H7" s="24" t="n">
         <v>0.63</v>
       </c>
-      <c r="I7" s="23" t="n">
+      <c r="I7" s="24" t="n">
         <v>0.65</v>
       </c>
-      <c r="J7" s="23" t="n">
+      <c r="J7" s="24" t="n">
         <v>0.65</v>
       </c>
-      <c r="K7" s="23" t="n">
+      <c r="K7" s="24" t="n">
         <v>0.65</v>
       </c>
-      <c r="L7" s="23" t="n">
+      <c r="L7" s="24" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -2204,71 +2229,71 @@
           <t>Research &amp; Development</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="21" t="n">
         <v>55</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="21" t="n">
         <v>65</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="21" t="n">
         <v>72</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="21" t="n">
         <v>74</v>
       </c>
-      <c r="J9" s="20" t="n">
+      <c r="J9" s="21" t="n">
         <v>76</v>
       </c>
-      <c r="K9" s="20" t="n">
+      <c r="K9" s="21" t="n">
         <v>78</v>
       </c>
-      <c r="L9" s="20" t="n">
+      <c r="L9" s="21" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  % of Revenue</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="25" t="n">
         <v>10000</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="25" t="n">
         <v>687.5</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="25" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="25" t="n">
         <v>53.8</v>
       </c>
-      <c r="H10" s="24" t="n">
+      <c r="H10" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="I10" s="24" t="n">
+      <c r="I10" s="25" t="n">
         <v>26.4</v>
       </c>
-      <c r="J10" s="24" t="n">
+      <c r="J10" s="25" t="n">
         <v>21.1</v>
       </c>
-      <c r="K10" s="24" t="n">
+      <c r="K10" s="25" t="n">
         <v>18.1</v>
       </c>
-      <c r="L10" s="24" t="n">
+      <c r="L10" s="25" t="n">
         <v>16.3</v>
       </c>
     </row>
@@ -2278,34 +2303,34 @@
           <t>General &amp; Administrative</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="21" t="n">
         <v>28</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <v>32</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="21" t="n">
         <v>34</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="21" t="n">
         <v>38</v>
       </c>
-      <c r="I11" s="20" t="n">
+      <c r="I11" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="K11" s="21" t="n">
         <v>41</v>
       </c>
-      <c r="L11" s="20" t="n">
+      <c r="L11" s="21" t="n">
         <v>42</v>
       </c>
     </row>
@@ -2315,34 +2340,34 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="I12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="20" t="n">
+      <c r="K12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L12" s="20" t="n">
+      <c r="L12" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2352,34 +2377,34 @@
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="26" t="n">
         <v>83</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <v>90</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <v>97</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="H13" s="25" t="n">
+      <c r="H13" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="I13" s="25" t="n">
+      <c r="I13" s="26" t="n">
         <v>119</v>
       </c>
-      <c r="J13" s="25" t="n">
+      <c r="J13" s="26" t="n">
         <v>121</v>
       </c>
-      <c r="K13" s="25" t="n">
+      <c r="K13" s="26" t="n">
         <v>124</v>
       </c>
-      <c r="L13" s="25" t="n">
+      <c r="L13" s="26" t="n">
         <v>127</v>
       </c>
     </row>
@@ -2396,71 +2421,71 @@
           <t>EBIT (Operating Income)</t>
         </is>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <v>-82.7</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="27" t="n">
         <v>-86</v>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="27" t="n">
         <v>-81.40000000000001</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="27" t="n">
         <v>-65.5</v>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="27" t="n">
         <v>-33</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="I15" s="27" t="n">
+      <c r="I15" s="28" t="n">
         <v>63</v>
       </c>
-      <c r="J15" s="27" t="n">
+      <c r="J15" s="28" t="n">
         <v>113</v>
       </c>
-      <c r="K15" s="27" t="n">
+      <c r="K15" s="28" t="n">
         <v>155.5</v>
       </c>
-      <c r="L15" s="27" t="n">
+      <c r="L15" s="28" t="n">
         <v>191.5</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT Margin %</t>
         </is>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="29" t="n">
         <v>-165.4</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="29" t="n">
         <v>-10.75</v>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="29" t="n">
         <v>-2.7133</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="29" t="n">
         <v>-0.9357</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="29" t="n">
         <v>-0.2538</v>
       </c>
-      <c r="H16" s="29" t="n">
+      <c r="H16" s="30" t="n">
         <v>0.055</v>
       </c>
-      <c r="I16" s="29" t="n">
+      <c r="I16" s="30" t="n">
         <v>0.225</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="J16" s="30" t="n">
         <v>0.3139</v>
       </c>
-      <c r="K16" s="29" t="n">
+      <c r="K16" s="30" t="n">
         <v>0.3616</v>
       </c>
-      <c r="L16" s="29" t="n">
+      <c r="L16" s="30" t="n">
         <v>0.3908</v>
       </c>
     </row>
@@ -2470,34 +2495,34 @@
           <t>NOPAT (EBIT × (1 – 25% tax))</t>
         </is>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>-82.7</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="27" t="n">
         <v>-86</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="27" t="n">
         <v>-81.40000000000001</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="27" t="n">
         <v>-65.5</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="27" t="n">
         <v>-33</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="28" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I17" s="27" t="n">
+      <c r="I17" s="28" t="n">
         <v>47.2</v>
       </c>
-      <c r="J17" s="27" t="n">
+      <c r="J17" s="28" t="n">
         <v>84.8</v>
       </c>
-      <c r="K17" s="27" t="n">
+      <c r="K17" s="28" t="n">
         <v>116.6</v>
       </c>
-      <c r="L17" s="27" t="n">
+      <c r="L17" s="28" t="n">
         <v>143.6</v>
       </c>
     </row>
@@ -2514,183 +2539,183 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="31" t="n">
         <v>-82.7</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="31" t="n">
         <v>-86</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="E19" s="31" t="n">
         <v>-81.40000000000001</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="31" t="n">
         <v>-65.5</v>
       </c>
-      <c r="G19" s="30" t="n">
+      <c r="G19" s="31" t="n">
         <v>-33</v>
       </c>
-      <c r="H19" s="30" t="n">
+      <c r="H19" s="31" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I19" s="30" t="n">
+      <c r="I19" s="31" t="n">
         <v>47.2</v>
       </c>
-      <c r="J19" s="30" t="n">
+      <c r="J19" s="31" t="n">
         <v>84.8</v>
       </c>
-      <c r="K19" s="30" t="n">
+      <c r="K19" s="31" t="n">
         <v>116.6</v>
       </c>
-      <c r="L19" s="30" t="n">
+      <c r="L19" s="31" t="n">
         <v>143.6</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  (+) Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="20" t="n">
+      <c r="D20" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="20" t="n">
+      <c r="E20" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="F20" s="20" t="n">
+      <c r="F20" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="20" t="n">
+      <c r="H20" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="I20" s="20" t="n">
+      <c r="I20" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="J20" s="20" t="n">
+      <c r="J20" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K20" s="20" t="n">
+      <c r="K20" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L20" s="20" t="n">
+      <c r="L20" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  (–) Capital Expenditures</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
+      <c r="C21" s="32" t="inlineStr">
         <is>
           <t>(12.0)</t>
         </is>
       </c>
-      <c r="D21" s="31" t="inlineStr">
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>(15.0)</t>
         </is>
       </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>(15.0)</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>(12.0)</t>
         </is>
       </c>
-      <c r="G21" s="31" t="inlineStr">
+      <c r="G21" s="32" t="inlineStr">
         <is>
           <t>(12.0)</t>
         </is>
       </c>
-      <c r="H21" s="31" t="inlineStr">
+      <c r="H21" s="32" t="inlineStr">
         <is>
           <t>(10.0)</t>
         </is>
       </c>
-      <c r="I21" s="31" t="inlineStr">
+      <c r="I21" s="32" t="inlineStr">
         <is>
           <t>(10.0)</t>
         </is>
       </c>
-      <c r="J21" s="31" t="inlineStr">
+      <c r="J21" s="32" t="inlineStr">
         <is>
           <t>(10.0)</t>
         </is>
       </c>
-      <c r="K21" s="31" t="inlineStr">
+      <c r="K21" s="32" t="inlineStr">
         <is>
           <t>(10.0)</t>
         </is>
       </c>
-      <c r="L21" s="31" t="inlineStr">
+      <c r="L21" s="32" t="inlineStr">
         <is>
           <t>(10.0)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  (–) Change in Net Working Capital</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>(0.0)</t>
         </is>
       </c>
-      <c r="D22" s="31" t="inlineStr">
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>(1.5)</t>
         </is>
       </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>(4.4)</t>
         </is>
       </c>
-      <c r="F22" s="31" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr">
         <is>
           <t>(8.0)</t>
         </is>
       </c>
-      <c r="G22" s="31" t="inlineStr">
+      <c r="G22" s="32" t="inlineStr">
         <is>
           <t>(12.0)</t>
         </is>
       </c>
-      <c r="H22" s="31" t="inlineStr">
+      <c r="H22" s="32" t="inlineStr">
         <is>
           <t>(14.0)</t>
         </is>
       </c>
-      <c r="I22" s="31" t="inlineStr">
+      <c r="I22" s="32" t="inlineStr">
         <is>
           <t>(16.0)</t>
         </is>
       </c>
-      <c r="J22" s="31" t="inlineStr">
+      <c r="J22" s="32" t="inlineStr">
         <is>
           <t>(16.0)</t>
         </is>
       </c>
-      <c r="K22" s="31" t="inlineStr">
+      <c r="K22" s="32" t="inlineStr">
         <is>
           <t>(14.0)</t>
         </is>
       </c>
-      <c r="L22" s="31" t="inlineStr">
+      <c r="L22" s="32" t="inlineStr">
         <is>
           <t>(12.0)</t>
         </is>
@@ -2702,39 +2727,47 @@
           <t>Unlevered Free Cash Flow</t>
         </is>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="33" t="n">
         <v>-89.7</v>
       </c>
-      <c r="D23" s="32" t="n">
+      <c r="D23" s="33" t="n">
         <v>-97.5</v>
       </c>
-      <c r="E23" s="32" t="n">
+      <c r="E23" s="33" t="n">
         <v>-95.8</v>
       </c>
-      <c r="F23" s="32" t="n">
+      <c r="F23" s="33" t="n">
         <v>-80.5</v>
       </c>
-      <c r="G23" s="32" t="n">
+      <c r="G23" s="33" t="n">
         <v>-52</v>
       </c>
-      <c r="H23" s="32" t="n">
+      <c r="H23" s="33" t="n">
         <v>-10.8</v>
       </c>
-      <c r="I23" s="25" t="n">
+      <c r="I23" s="26" t="n">
         <v>26.2</v>
       </c>
-      <c r="J23" s="25" t="n">
+      <c r="J23" s="26" t="n">
         <v>63.8</v>
       </c>
-      <c r="K23" s="25" t="n">
+      <c r="K23" s="26" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="L23" s="25" t="n">
+      <c r="L23" s="26" t="n">
         <v>126.6</v>
       </c>
     </row>
+    <row r="25" ht="12" customHeight="1">
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Francisco Rodriguez  |  Financial Modeling Portfolio  |  github.com/Azyo1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B25:L25"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B14:L14"/>
     <mergeCell ref="B18:L18"/>
@@ -2751,7 +2784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L33"/>
+  <dimension ref="B1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2776,7 +2809,7 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
@@ -2845,7 +2878,7 @@
           <t>Risk-Free Rate</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -2855,7 +2888,7 @@
           <t>Equity Risk Premium</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -2865,7 +2898,7 @@
           <t>Beta (Relevered)</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -2875,7 +2908,7 @@
           <t>Size &amp; Illiquidity Premium</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2885,7 +2918,7 @@
           <t>Cost of Equity / WACC</t>
         </is>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="34" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -2902,34 +2935,34 @@
           <t>Unlevered FCF ($M)</t>
         </is>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="31" t="n">
         <v>-84.7</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="31" t="n">
         <v>-92.5</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="31" t="n">
         <v>-90.8</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="31" t="n">
         <v>-75.5</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="31" t="n">
         <v>-47</v>
       </c>
-      <c r="H11" s="30" t="n">
+      <c r="H11" s="31" t="n">
         <v>-7</v>
       </c>
-      <c r="I11" s="30" t="n">
+      <c r="I11" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="J11" s="30" t="n">
+      <c r="J11" s="31" t="n">
         <v>67.5</v>
       </c>
-      <c r="K11" s="30" t="n">
+      <c r="K11" s="31" t="n">
         <v>101.4</v>
       </c>
-      <c r="L11" s="30" t="n">
+      <c r="L11" s="31" t="n">
         <v>130.4</v>
       </c>
     </row>
@@ -2939,34 +2972,34 @@
           <t>Discount Period (n)</t>
         </is>
       </c>
-      <c r="C12" s="34" t="n">
+      <c r="C12" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="34" t="n">
+      <c r="E12" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="34" t="n">
+      <c r="H12" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="I12" s="34" t="n">
+      <c r="I12" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="J12" s="34" t="n">
+      <c r="J12" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="K12" s="34" t="n">
+      <c r="K12" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="L12" s="34" t="n">
+      <c r="L12" s="35" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2976,34 +3009,34 @@
           <t>PV Factor  [1/(1+WACC)^n]</t>
         </is>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="36" t="n">
         <v>0.833333</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="36" t="n">
         <v>0.694444</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="36" t="n">
         <v>0.578704</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="36" t="n">
         <v>0.482253</v>
       </c>
-      <c r="G13" s="35" t="n">
+      <c r="G13" s="36" t="n">
         <v>0.401878</v>
       </c>
-      <c r="H13" s="35" t="n">
+      <c r="H13" s="36" t="n">
         <v>0.334898</v>
       </c>
-      <c r="I13" s="35" t="n">
+      <c r="I13" s="36" t="n">
         <v>0.279082</v>
       </c>
-      <c r="J13" s="35" t="n">
+      <c r="J13" s="36" t="n">
         <v>0.232568</v>
       </c>
-      <c r="K13" s="35" t="n">
+      <c r="K13" s="36" t="n">
         <v>0.193807</v>
       </c>
-      <c r="L13" s="35" t="n">
+      <c r="L13" s="36" t="n">
         <v>0.161506</v>
       </c>
     </row>
@@ -3013,34 +3046,34 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>-70.59999999999999</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="27" t="n">
         <v>-64.2</v>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="27" t="n">
         <v>-52.5</v>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="27" t="n">
         <v>-36.4</v>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G14" s="27" t="n">
         <v>-18.9</v>
       </c>
-      <c r="H14" s="26" t="n">
+      <c r="H14" s="27" t="n">
         <v>-2.3</v>
       </c>
-      <c r="I14" s="27" t="n">
+      <c r="I14" s="28" t="n">
         <v>8.4</v>
       </c>
-      <c r="J14" s="27" t="n">
+      <c r="J14" s="28" t="n">
         <v>15.7</v>
       </c>
-      <c r="K14" s="27" t="n">
+      <c r="K14" s="28" t="n">
         <v>19.7</v>
       </c>
-      <c r="L14" s="27" t="n">
+      <c r="L14" s="28" t="n">
         <v>21.1</v>
       </c>
     </row>
@@ -3050,7 +3083,7 @@
           <t>Sum of PV FCFs</t>
         </is>
       </c>
-      <c r="C15" s="32" t="n">
+      <c r="C15" s="33" t="n">
         <v>-180</v>
       </c>
     </row>
@@ -3067,7 +3100,7 @@
           <t>Terminal Year Revenue ($M)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="21" t="n">
         <v>490</v>
       </c>
     </row>
@@ -3077,7 +3110,7 @@
           <t>Terminal EV / Revenue Multiple</t>
         </is>
       </c>
-      <c r="C19" s="36" t="n">
+      <c r="C19" s="37" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3087,7 +3120,7 @@
           <t>Terminal Enterprise Value ($M)</t>
         </is>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="26" t="n">
         <v>3920</v>
       </c>
     </row>
@@ -3097,7 +3130,7 @@
           <t>Discount Factor (Year 10)</t>
         </is>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="36" t="n">
         <v>0.161506</v>
       </c>
     </row>
@@ -3107,7 +3140,7 @@
           <t>PV of Terminal Value ($M)</t>
         </is>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C22" s="28" t="n">
         <v>633.1</v>
       </c>
     </row>
@@ -3124,7 +3157,7 @@
           <t>Sum of PV FCFs ($M)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="21" t="n">
         <v>-180</v>
       </c>
     </row>
@@ -3134,7 +3167,7 @@
           <t>(+) PV of Terminal Value ($M)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="21" t="n">
         <v>633.1</v>
       </c>
     </row>
@@ -3144,7 +3177,7 @@
           <t>Enterprise Value ($M)</t>
         </is>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="26" t="n">
         <v>453.1</v>
       </c>
     </row>
@@ -3154,7 +3187,7 @@
           <t>(+) Net Cash ($M)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="21" t="n">
         <v>156.1</v>
       </c>
     </row>
@@ -3164,7 +3197,7 @@
           <t>Equity Value ($M)</t>
         </is>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="26" t="n">
         <v>609.2</v>
       </c>
     </row>
@@ -3174,7 +3207,7 @@
           <t>(÷) Shares Outstanding (M)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="21" t="n">
         <v>126.6</v>
       </c>
     </row>
@@ -3184,7 +3217,7 @@
           <t>Intrinsic Value per Share</t>
         </is>
       </c>
-      <c r="C31" s="37" t="n">
+      <c r="C31" s="38" t="n">
         <v>4.81</v>
       </c>
     </row>
@@ -3194,7 +3227,7 @@
           <t>Current Price</t>
         </is>
       </c>
-      <c r="C32" s="38" t="n">
+      <c r="C32" s="39" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -3204,13 +3237,21 @@
           <t>Upside / (Downside)</t>
         </is>
       </c>
-      <c r="C33" s="39" t="n">
+      <c r="C33" s="40" t="n">
         <v>0.8151</v>
       </c>
     </row>
+    <row r="35" ht="12" customHeight="1">
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Francisco Rodriguez  |  Financial Modeling Portfolio  |  github.com/Azyo1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B35:L35"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="B10:L10"/>
@@ -3227,7 +3268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:K33"/>
+  <dimension ref="B1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3258,7 +3299,7 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>WACC ↓  |  EV/Rev →</t>
         </is>
@@ -3310,28 +3351,28 @@
           <t>14%</t>
         </is>
       </c>
-      <c r="C5" s="41" t="n">
+      <c r="C5" s="42" t="n">
         <v>5.05</v>
       </c>
-      <c r="D5" s="42" t="n">
+      <c r="D5" s="43" t="n">
         <v>6.1</v>
       </c>
-      <c r="E5" s="42" t="n">
+      <c r="E5" s="43" t="n">
         <v>7.14</v>
       </c>
-      <c r="F5" s="42" t="n">
+      <c r="F5" s="43" t="n">
         <v>8.19</v>
       </c>
-      <c r="G5" s="42" t="n">
+      <c r="G5" s="43" t="n">
         <v>9.23</v>
       </c>
-      <c r="H5" s="42" t="n">
+      <c r="H5" s="43" t="n">
         <v>10.27</v>
       </c>
-      <c r="I5" s="42" t="n">
+      <c r="I5" s="43" t="n">
         <v>11.32</v>
       </c>
-      <c r="J5" s="42" t="n">
+      <c r="J5" s="43" t="n">
         <v>12.36</v>
       </c>
     </row>
@@ -3341,28 +3382,28 @@
           <t>16%</t>
         </is>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="42" t="n">
         <v>4.2</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="42" t="n">
         <v>5.08</v>
       </c>
-      <c r="E6" s="41" t="n">
+      <c r="E6" s="42" t="n">
         <v>5.96</v>
       </c>
-      <c r="F6" s="42" t="n">
+      <c r="F6" s="43" t="n">
         <v>6.83</v>
       </c>
-      <c r="G6" s="42" t="n">
+      <c r="G6" s="43" t="n">
         <v>7.71</v>
       </c>
-      <c r="H6" s="42" t="n">
+      <c r="H6" s="43" t="n">
         <v>8.59</v>
       </c>
-      <c r="I6" s="42" t="n">
+      <c r="I6" s="43" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="J6" s="42" t="n">
+      <c r="J6" s="43" t="n">
         <v>10.34</v>
       </c>
     </row>
@@ -3372,28 +3413,28 @@
           <t>17%</t>
         </is>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="C7" s="44" t="n">
         <v>3.84</v>
       </c>
-      <c r="D7" s="41" t="n">
+      <c r="D7" s="42" t="n">
         <v>4.64</v>
       </c>
-      <c r="E7" s="41" t="n">
+      <c r="E7" s="42" t="n">
         <v>5.45</v>
       </c>
-      <c r="F7" s="42" t="n">
+      <c r="F7" s="43" t="n">
         <v>6.25</v>
       </c>
-      <c r="G7" s="42" t="n">
+      <c r="G7" s="43" t="n">
         <v>7.06</v>
       </c>
-      <c r="H7" s="42" t="n">
+      <c r="H7" s="43" t="n">
         <v>7.86</v>
       </c>
-      <c r="I7" s="42" t="n">
+      <c r="I7" s="43" t="n">
         <v>8.67</v>
       </c>
-      <c r="J7" s="42" t="n">
+      <c r="J7" s="43" t="n">
         <v>9.470000000000001</v>
       </c>
     </row>
@@ -3403,28 +3444,28 @@
           <t>18%</t>
         </is>
       </c>
-      <c r="C8" s="43" t="n">
+      <c r="C8" s="44" t="n">
         <v>3.51</v>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="42" t="n">
         <v>4.25</v>
       </c>
-      <c r="E8" s="41" t="n">
+      <c r="E8" s="42" t="n">
         <v>4.98</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="42" t="n">
         <v>5.72</v>
       </c>
-      <c r="G8" s="42" t="n">
+      <c r="G8" s="43" t="n">
         <v>6.46</v>
       </c>
-      <c r="H8" s="42" t="n">
+      <c r="H8" s="43" t="n">
         <v>7.2</v>
       </c>
-      <c r="I8" s="42" t="n">
+      <c r="I8" s="43" t="n">
         <v>7.94</v>
       </c>
-      <c r="J8" s="42" t="n">
+      <c r="J8" s="43" t="n">
         <v>8.68</v>
       </c>
     </row>
@@ -3434,28 +3475,28 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="C9" s="43" t="n">
+      <c r="C9" s="44" t="n">
         <v>2.93</v>
       </c>
-      <c r="D9" s="43" t="n">
+      <c r="D9" s="44" t="n">
         <v>3.56</v>
       </c>
-      <c r="E9" s="41" t="n">
+      <c r="E9" s="42" t="n">
         <v>4.19</v>
       </c>
-      <c r="F9" s="41" t="n">
+      <c r="F9" s="42" t="n">
         <v>4.81</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="42" t="n">
         <v>5.44</v>
       </c>
-      <c r="H9" s="42" t="n">
+      <c r="H9" s="43" t="n">
         <v>6.06</v>
       </c>
-      <c r="I9" s="42" t="n">
+      <c r="I9" s="43" t="n">
         <v>6.69</v>
       </c>
-      <c r="J9" s="42" t="n">
+      <c r="J9" s="43" t="n">
         <v>7.31</v>
       </c>
     </row>
@@ -3465,28 +3506,28 @@
           <t>22%</t>
         </is>
       </c>
-      <c r="C10" s="44" t="n">
+      <c r="C10" s="45" t="n">
         <v>2.47</v>
       </c>
-      <c r="D10" s="43" t="n">
+      <c r="D10" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="43" t="n">
+      <c r="E10" s="44" t="n">
         <v>3.53</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="42" t="n">
         <v>4.06</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="42" t="n">
         <v>4.59</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="42" t="n">
         <v>5.12</v>
       </c>
-      <c r="I10" s="41" t="n">
+      <c r="I10" s="42" t="n">
         <v>5.65</v>
       </c>
-      <c r="J10" s="42" t="n">
+      <c r="J10" s="43" t="n">
         <v>6.18</v>
       </c>
     </row>
@@ -3496,28 +3537,28 @@
           <t>24%</t>
         </is>
       </c>
-      <c r="C11" s="44" t="n">
+      <c r="C11" s="45" t="n">
         <v>2.08</v>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="45" t="n">
         <v>2.53</v>
       </c>
-      <c r="E11" s="43" t="n">
+      <c r="E11" s="44" t="n">
         <v>2.98</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="44" t="n">
         <v>3.43</v>
       </c>
-      <c r="G11" s="43" t="n">
+      <c r="G11" s="44" t="n">
         <v>3.88</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H11" s="42" t="n">
         <v>4.33</v>
       </c>
-      <c r="I11" s="41" t="n">
+      <c r="I11" s="42" t="n">
         <v>4.79</v>
       </c>
-      <c r="J11" s="41" t="n">
+      <c r="J11" s="42" t="n">
         <v>5.24</v>
       </c>
     </row>
@@ -3527,33 +3568,33 @@
           <t>26%</t>
         </is>
       </c>
-      <c r="C12" s="44" t="n">
+      <c r="C12" s="45" t="n">
         <v>1.77</v>
       </c>
-      <c r="D12" s="44" t="n">
+      <c r="D12" s="45" t="n">
         <v>2.15</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="45" t="n">
         <v>2.54</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F12" s="44" t="n">
         <v>2.92</v>
       </c>
-      <c r="G12" s="43" t="n">
+      <c r="G12" s="44" t="n">
         <v>3.3</v>
       </c>
-      <c r="H12" s="43" t="n">
+      <c r="H12" s="44" t="n">
         <v>3.69</v>
       </c>
-      <c r="I12" s="41" t="n">
+      <c r="I12" s="42" t="n">
         <v>4.07</v>
       </c>
-      <c r="J12" s="41" t="n">
+      <c r="J12" s="42" t="n">
         <v>4.45</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="45" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>★ Base case: 20% WACC, 8.0x EV/Revenue, $490M terminal revenue → $4.81/share. Green = above current price ($2.65). Dark green = 2×+ current price.</t>
         </is>
@@ -3567,7 +3608,7 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>WACC ↓  |  Term. Rev →</t>
         </is>
@@ -3619,28 +3660,28 @@
           <t>14%</t>
         </is>
       </c>
-      <c r="C19" s="44" t="n">
+      <c r="C19" s="45" t="n">
         <v>2.39</v>
       </c>
-      <c r="D19" s="41" t="n">
+      <c r="D19" s="42" t="n">
         <v>4.1</v>
       </c>
-      <c r="E19" s="41" t="n">
+      <c r="E19" s="42" t="n">
         <v>5.8</v>
       </c>
-      <c r="F19" s="42" t="n">
+      <c r="F19" s="43" t="n">
         <v>8.19</v>
       </c>
-      <c r="G19" s="42" t="n">
+      <c r="G19" s="43" t="n">
         <v>10.06</v>
       </c>
-      <c r="H19" s="42" t="n">
+      <c r="H19" s="43" t="n">
         <v>11.77</v>
       </c>
-      <c r="I19" s="42" t="n">
+      <c r="I19" s="43" t="n">
         <v>13.47</v>
       </c>
-      <c r="J19" s="42" t="n">
+      <c r="J19" s="43" t="n">
         <v>16.03</v>
       </c>
     </row>
@@ -3650,28 +3691,28 @@
           <t>16%</t>
         </is>
       </c>
-      <c r="C20" s="44" t="n">
+      <c r="C20" s="45" t="n">
         <v>1.96</v>
       </c>
-      <c r="D20" s="43" t="n">
+      <c r="D20" s="44" t="n">
         <v>3.4</v>
       </c>
-      <c r="E20" s="41" t="n">
+      <c r="E20" s="42" t="n">
         <v>4.83</v>
       </c>
-      <c r="F20" s="42" t="n">
+      <c r="F20" s="43" t="n">
         <v>6.83</v>
       </c>
-      <c r="G20" s="42" t="n">
+      <c r="G20" s="43" t="n">
         <v>8.41</v>
       </c>
-      <c r="H20" s="42" t="n">
+      <c r="H20" s="43" t="n">
         <v>9.84</v>
       </c>
-      <c r="I20" s="42" t="n">
+      <c r="I20" s="43" t="n">
         <v>11.28</v>
       </c>
-      <c r="J20" s="42" t="n">
+      <c r="J20" s="43" t="n">
         <v>13.42</v>
       </c>
     </row>
@@ -3681,28 +3722,28 @@
           <t>17%</t>
         </is>
       </c>
-      <c r="C21" s="44" t="n">
+      <c r="C21" s="45" t="n">
         <v>1.78</v>
       </c>
-      <c r="D21" s="43" t="n">
+      <c r="D21" s="44" t="n">
         <v>3.1</v>
       </c>
-      <c r="E21" s="41" t="n">
+      <c r="E21" s="42" t="n">
         <v>4.41</v>
       </c>
-      <c r="F21" s="42" t="n">
+      <c r="F21" s="43" t="n">
         <v>6.25</v>
       </c>
-      <c r="G21" s="42" t="n">
+      <c r="G21" s="43" t="n">
         <v>7.7</v>
       </c>
-      <c r="H21" s="42" t="n">
+      <c r="H21" s="43" t="n">
         <v>9.01</v>
       </c>
-      <c r="I21" s="42" t="n">
+      <c r="I21" s="43" t="n">
         <v>10.33</v>
       </c>
-      <c r="J21" s="42" t="n">
+      <c r="J21" s="43" t="n">
         <v>12.3</v>
       </c>
     </row>
@@ -3712,28 +3753,28 @@
           <t>18%</t>
         </is>
       </c>
-      <c r="C22" s="44" t="n">
+      <c r="C22" s="45" t="n">
         <v>1.62</v>
       </c>
-      <c r="D22" s="43" t="n">
+      <c r="D22" s="44" t="n">
         <v>2.83</v>
       </c>
-      <c r="E22" s="41" t="n">
+      <c r="E22" s="42" t="n">
         <v>4.03</v>
       </c>
-      <c r="F22" s="41" t="n">
+      <c r="F22" s="42" t="n">
         <v>5.72</v>
       </c>
-      <c r="G22" s="42" t="n">
+      <c r="G22" s="43" t="n">
         <v>7.05</v>
       </c>
-      <c r="H22" s="42" t="n">
+      <c r="H22" s="43" t="n">
         <v>8.26</v>
       </c>
-      <c r="I22" s="42" t="n">
+      <c r="I22" s="43" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="J22" s="42" t="n">
+      <c r="J22" s="43" t="n">
         <v>11.28</v>
       </c>
     </row>
@@ -3743,28 +3784,28 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="C23" s="46" t="n">
+      <c r="C23" s="47" t="n">
         <v>1.34</v>
       </c>
-      <c r="D23" s="44" t="n">
+      <c r="D23" s="45" t="n">
         <v>2.36</v>
       </c>
-      <c r="E23" s="43" t="n">
+      <c r="E23" s="44" t="n">
         <v>3.38</v>
       </c>
-      <c r="F23" s="41" t="n">
+      <c r="F23" s="42" t="n">
         <v>4.81</v>
       </c>
-      <c r="G23" s="41" t="n">
+      <c r="G23" s="42" t="n">
         <v>5.93</v>
       </c>
-      <c r="H23" s="42" t="n">
+      <c r="H23" s="43" t="n">
         <v>6.95</v>
       </c>
-      <c r="I23" s="42" t="n">
+      <c r="I23" s="43" t="n">
         <v>7.97</v>
       </c>
-      <c r="J23" s="42" t="n">
+      <c r="J23" s="43" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -3774,28 +3815,28 @@
           <t>22%</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n">
+      <c r="C24" s="47" t="n">
         <v>1.12</v>
       </c>
-      <c r="D24" s="44" t="n">
+      <c r="D24" s="45" t="n">
         <v>1.98</v>
       </c>
-      <c r="E24" s="43" t="n">
+      <c r="E24" s="44" t="n">
         <v>2.85</v>
       </c>
-      <c r="F24" s="41" t="n">
+      <c r="F24" s="42" t="n">
         <v>4.06</v>
       </c>
-      <c r="G24" s="41" t="n">
+      <c r="G24" s="42" t="n">
         <v>5.01</v>
       </c>
-      <c r="H24" s="41" t="n">
+      <c r="H24" s="42" t="n">
         <v>5.87</v>
       </c>
-      <c r="I24" s="42" t="n">
+      <c r="I24" s="43" t="n">
         <v>6.74</v>
       </c>
-      <c r="J24" s="42" t="n">
+      <c r="J24" s="43" t="n">
         <v>8.039999999999999</v>
       </c>
     </row>
@@ -3805,28 +3846,28 @@
           <t>24%</t>
         </is>
       </c>
-      <c r="C25" s="46" t="n">
+      <c r="C25" s="47" t="n">
         <v>0.93</v>
       </c>
-      <c r="D25" s="44" t="n">
+      <c r="D25" s="45" t="n">
         <v>1.67</v>
       </c>
-      <c r="E25" s="44" t="n">
+      <c r="E25" s="45" t="n">
         <v>2.4</v>
       </c>
-      <c r="F25" s="43" t="n">
+      <c r="F25" s="44" t="n">
         <v>3.43</v>
       </c>
-      <c r="G25" s="41" t="n">
+      <c r="G25" s="42" t="n">
         <v>4.24</v>
       </c>
-      <c r="H25" s="41" t="n">
+      <c r="H25" s="42" t="n">
         <v>4.98</v>
       </c>
-      <c r="I25" s="41" t="n">
+      <c r="I25" s="42" t="n">
         <v>5.71</v>
       </c>
-      <c r="J25" s="42" t="n">
+      <c r="J25" s="43" t="n">
         <v>6.82</v>
       </c>
     </row>
@@ -3836,28 +3877,28 @@
           <t>26%</t>
         </is>
       </c>
-      <c r="C26" s="46" t="n">
+      <c r="C26" s="47" t="n">
         <v>0.79</v>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="47" t="n">
         <v>1.42</v>
       </c>
-      <c r="E26" s="44" t="n">
+      <c r="E26" s="45" t="n">
         <v>2.04</v>
       </c>
-      <c r="F26" s="43" t="n">
+      <c r="F26" s="44" t="n">
         <v>2.92</v>
       </c>
-      <c r="G26" s="43" t="n">
+      <c r="G26" s="44" t="n">
         <v>3.61</v>
       </c>
-      <c r="H26" s="41" t="n">
+      <c r="H26" s="42" t="n">
         <v>4.23</v>
       </c>
-      <c r="I26" s="41" t="n">
+      <c r="I26" s="42" t="n">
         <v>4.86</v>
       </c>
-      <c r="J26" s="41" t="n">
+      <c r="J26" s="42" t="n">
         <v>5.8</v>
       </c>
     </row>
@@ -4056,9 +4097,17 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="12" customHeight="1">
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Francisco Rodriguez  |  Financial Modeling Portfolio  |  github.com/Azyo1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B35:L35"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B14:J14"/>
